--- a/pandemic-loss-modeling/data/epidemics_marani_240816.xlsx
+++ b/pandemic-loss-modeling/data/epidemics_marani_240816.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lichong/Desktop/RA 23F Epidemic/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE33A98-F751-2440-9FAE-1B195F21E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2295CB99-6C51-4040-B16A-D8FC83BA3A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="22620" windowHeight="14420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1207,9 +1207,6 @@
     <t>kyasanur forest disease</t>
   </si>
   <si>
-    <t>hemorragic fever</t>
-  </si>
-  <si>
     <t>ebola</t>
   </si>
   <si>
@@ -1310,6 +1307,9 @@
   </si>
   <si>
     <t>animalcontact/bite</t>
+  </si>
+  <si>
+    <t>hemorrhagic fever</t>
   </si>
 </sst>
 </file>
@@ -1897,10 +1897,10 @@
         <v>361</v>
       </c>
       <c r="J5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -1944,10 +1944,10 @@
         <v>362</v>
       </c>
       <c r="J6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -2226,10 +2226,10 @@
         <v>361</v>
       </c>
       <c r="J12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -2273,10 +2273,10 @@
         <v>363</v>
       </c>
       <c r="J13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2320,10 +2320,10 @@
         <v>361</v>
       </c>
       <c r="J14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L14">
         <v>1</v>
@@ -2461,10 +2461,10 @@
         <v>364</v>
       </c>
       <c r="J17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>363</v>
       </c>
       <c r="J20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K20" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2790,10 +2790,10 @@
         <v>364</v>
       </c>
       <c r="J24" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K24" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2884,10 +2884,10 @@
         <v>361</v>
       </c>
       <c r="J26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K26" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L26">
         <v>1</v>
@@ -2931,10 +2931,10 @@
         <v>366</v>
       </c>
       <c r="J27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -3025,10 +3025,10 @@
         <v>364</v>
       </c>
       <c r="J29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K29" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>361</v>
       </c>
       <c r="J31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K31" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L31">
         <v>1</v>
@@ -3213,10 +3213,10 @@
         <v>364</v>
       </c>
       <c r="J33" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K33" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3307,10 +3307,10 @@
         <v>364</v>
       </c>
       <c r="J35" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K35" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3401,10 +3401,10 @@
         <v>363</v>
       </c>
       <c r="J37" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K37" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3448,10 +3448,10 @@
         <v>363</v>
       </c>
       <c r="J38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3542,10 +3542,10 @@
         <v>364</v>
       </c>
       <c r="J40" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K40" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -3683,10 +3683,10 @@
         <v>363</v>
       </c>
       <c r="J43" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K43" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>367</v>
       </c>
       <c r="J44" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K44" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>366</v>
       </c>
       <c r="J45" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K45" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -3824,10 +3824,10 @@
         <v>364</v>
       </c>
       <c r="J46" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K46" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -3871,10 +3871,10 @@
         <v>368</v>
       </c>
       <c r="J47" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K47" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -3965,10 +3965,10 @@
         <v>361</v>
       </c>
       <c r="J49" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K49" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L49">
         <v>1</v>
@@ -4012,10 +4012,10 @@
         <v>362</v>
       </c>
       <c r="J50" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K50" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L50">
         <v>1</v>
@@ -4059,10 +4059,10 @@
         <v>367</v>
       </c>
       <c r="J51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>363</v>
       </c>
       <c r="J53" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K53" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4200,10 +4200,10 @@
         <v>361</v>
       </c>
       <c r="J54" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K54" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L54">
         <v>1</v>
@@ -4247,10 +4247,10 @@
         <v>364</v>
       </c>
       <c r="J55" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K55" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4294,10 +4294,10 @@
         <v>361</v>
       </c>
       <c r="J56" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K56" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -4435,10 +4435,10 @@
         <v>364</v>
       </c>
       <c r="J59" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K59" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -4482,10 +4482,10 @@
         <v>361</v>
       </c>
       <c r="J60" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K60" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L60">
         <v>1</v>
@@ -4529,10 +4529,10 @@
         <v>363</v>
       </c>
       <c r="J61" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K61" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -4576,10 +4576,10 @@
         <v>369</v>
       </c>
       <c r="J62" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K62" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L62">
         <v>1</v>
@@ -4670,10 +4670,10 @@
         <v>363</v>
       </c>
       <c r="J64" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K64" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         <v>363</v>
       </c>
       <c r="J70" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K70" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>361</v>
       </c>
       <c r="J72" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K72" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L72">
         <v>1</v>
@@ -5093,10 +5093,10 @@
         <v>364</v>
       </c>
       <c r="J73" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K73" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -5140,10 +5140,10 @@
         <v>363</v>
       </c>
       <c r="J74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K74" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -5234,10 +5234,10 @@
         <v>363</v>
       </c>
       <c r="J76" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K76" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -5328,10 +5328,10 @@
         <v>363</v>
       </c>
       <c r="J78" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K78" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>361</v>
       </c>
       <c r="J79" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K79" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L79">
         <v>1</v>
@@ -5422,10 +5422,10 @@
         <v>364</v>
       </c>
       <c r="J80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K80" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -5469,10 +5469,10 @@
         <v>361</v>
       </c>
       <c r="J81" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K81" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L81">
         <v>1</v>
@@ -5563,10 +5563,10 @@
         <v>369</v>
       </c>
       <c r="J83" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K83" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L83">
         <v>1</v>
@@ -5610,10 +5610,10 @@
         <v>363</v>
       </c>
       <c r="J84" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K84" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -5704,10 +5704,10 @@
         <v>364</v>
       </c>
       <c r="J86" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K86" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -5798,10 +5798,10 @@
         <v>364</v>
       </c>
       <c r="J88" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K88" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -5845,10 +5845,10 @@
         <v>370</v>
       </c>
       <c r="J89" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K89" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L89">
         <v>1</v>
@@ -5892,10 +5892,10 @@
         <v>361</v>
       </c>
       <c r="J90" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K90" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L90">
         <v>1</v>
@@ -5986,10 +5986,10 @@
         <v>363</v>
       </c>
       <c r="J92" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K92" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6033,10 +6033,10 @@
         <v>370</v>
       </c>
       <c r="J93" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K93" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L93">
         <v>1</v>
@@ -6127,10 +6127,10 @@
         <v>361</v>
       </c>
       <c r="J95" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K95" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L95">
         <v>1</v>
@@ -6174,10 +6174,10 @@
         <v>364</v>
       </c>
       <c r="J96" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K96" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>363</v>
       </c>
       <c r="J97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K97" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>370</v>
       </c>
       <c r="J100" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K100" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L100">
         <v>1</v>
@@ -6503,10 +6503,10 @@
         <v>361</v>
       </c>
       <c r="J103" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K103" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L103">
         <v>1</v>
@@ -6550,10 +6550,10 @@
         <v>363</v>
       </c>
       <c r="J104" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K104" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -6644,10 +6644,10 @@
         <v>363</v>
       </c>
       <c r="J106" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -6691,10 +6691,10 @@
         <v>363</v>
       </c>
       <c r="J107" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K107" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -6785,10 +6785,10 @@
         <v>361</v>
       </c>
       <c r="J109" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K109" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -6879,10 +6879,10 @@
         <v>371</v>
       </c>
       <c r="J111" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K111" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L111">
         <v>1</v>
@@ -6926,10 +6926,10 @@
         <v>364</v>
       </c>
       <c r="J112" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K112" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -6973,10 +6973,10 @@
         <v>372</v>
       </c>
       <c r="J113" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K113" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -7020,10 +7020,10 @@
         <v>363</v>
       </c>
       <c r="J114" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K114" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -7067,10 +7067,10 @@
         <v>369</v>
       </c>
       <c r="J115" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K115" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -7208,10 +7208,10 @@
         <v>370</v>
       </c>
       <c r="J118" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K118" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -7255,10 +7255,10 @@
         <v>370</v>
       </c>
       <c r="J119" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K119" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L119">
         <v>1</v>
@@ -7302,10 +7302,10 @@
         <v>361</v>
       </c>
       <c r="J120" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K120" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L120">
         <v>1</v>
@@ -7396,10 +7396,10 @@
         <v>364</v>
       </c>
       <c r="J122" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K122" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -7443,10 +7443,10 @@
         <v>363</v>
       </c>
       <c r="J123" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K123" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -7490,10 +7490,10 @@
         <v>370</v>
       </c>
       <c r="J124" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K124" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L124">
         <v>1</v>
@@ -7584,10 +7584,10 @@
         <v>361</v>
       </c>
       <c r="J126" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K126" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L126">
         <v>1</v>
@@ -7631,10 +7631,10 @@
         <v>369</v>
       </c>
       <c r="J127" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K127" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L127">
         <v>1</v>
@@ -7678,10 +7678,10 @@
         <v>362</v>
       </c>
       <c r="J128" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K128" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L128">
         <v>1</v>
@@ -7725,10 +7725,10 @@
         <v>364</v>
       </c>
       <c r="J129" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K129" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -7772,10 +7772,10 @@
         <v>364</v>
       </c>
       <c r="J130" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K130" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -7819,10 +7819,10 @@
         <v>370</v>
       </c>
       <c r="J131" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K131" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L131">
         <v>1</v>
@@ -7866,10 +7866,10 @@
         <v>362</v>
       </c>
       <c r="J132" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K132" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L132">
         <v>1</v>
@@ -7913,10 +7913,10 @@
         <v>361</v>
       </c>
       <c r="J133" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K133" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L133">
         <v>1</v>
@@ -8007,10 +8007,10 @@
         <v>361</v>
       </c>
       <c r="J135" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K135" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L135">
         <v>1</v>
@@ -8148,10 +8148,10 @@
         <v>363</v>
       </c>
       <c r="J138" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K138" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L138">
         <v>0</v>
@@ -8195,10 +8195,10 @@
         <v>361</v>
       </c>
       <c r="J139" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K139" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L139">
         <v>1</v>
@@ -8336,10 +8336,10 @@
         <v>364</v>
       </c>
       <c r="J142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K142" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L142">
         <v>0</v>
@@ -8430,10 +8430,10 @@
         <v>370</v>
       </c>
       <c r="J144" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K144" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L144">
         <v>1</v>
@@ -8477,10 +8477,10 @@
         <v>362</v>
       </c>
       <c r="J145" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K145" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L145">
         <v>1</v>
@@ -8524,10 +8524,10 @@
         <v>369</v>
       </c>
       <c r="J146" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K146" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L146">
         <v>1</v>
@@ -8571,10 +8571,10 @@
         <v>370</v>
       </c>
       <c r="J147" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K147" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -8618,10 +8618,10 @@
         <v>362</v>
       </c>
       <c r="J148" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K148" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L148">
         <v>1</v>
@@ -8665,10 +8665,10 @@
         <v>361</v>
       </c>
       <c r="J149" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L149">
         <v>1</v>
@@ -8712,10 +8712,10 @@
         <v>364</v>
       </c>
       <c r="J150" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K150" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -8759,10 +8759,10 @@
         <v>367</v>
       </c>
       <c r="J151" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K151" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L151">
         <v>0</v>
@@ -8806,10 +8806,10 @@
         <v>366</v>
       </c>
       <c r="J152" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K152" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -8853,10 +8853,10 @@
         <v>363</v>
       </c>
       <c r="J153" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K153" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -8900,10 +8900,10 @@
         <v>373</v>
       </c>
       <c r="J154" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>370</v>
       </c>
       <c r="J155" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K155" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L155">
         <v>1</v>
@@ -8994,10 +8994,10 @@
         <v>362</v>
       </c>
       <c r="J156" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K156" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L156">
         <v>1</v>
@@ -9041,10 +9041,10 @@
         <v>364</v>
       </c>
       <c r="J157" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K157" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -9088,10 +9088,10 @@
         <v>374</v>
       </c>
       <c r="J158" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K158" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -9135,10 +9135,10 @@
         <v>370</v>
       </c>
       <c r="J159" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K159" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L159">
         <v>1</v>
@@ -9182,10 +9182,10 @@
         <v>375</v>
       </c>
       <c r="J160" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K160" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -9229,10 +9229,10 @@
         <v>364</v>
       </c>
       <c r="J161" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K161" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -9276,10 +9276,10 @@
         <v>362</v>
       </c>
       <c r="J162" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K162" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L162">
         <v>1</v>
@@ -9323,10 +9323,10 @@
         <v>370</v>
       </c>
       <c r="J163" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K163" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L163">
         <v>1</v>
@@ -9370,10 +9370,10 @@
         <v>370</v>
       </c>
       <c r="J164" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K164" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L164">
         <v>1</v>
@@ -9464,10 +9464,10 @@
         <v>367</v>
       </c>
       <c r="J166" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K166" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L166">
         <v>0</v>
@@ -9511,10 +9511,10 @@
         <v>364</v>
       </c>
       <c r="J167" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K167" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L167">
         <v>0</v>
@@ -9558,10 +9558,10 @@
         <v>361</v>
       </c>
       <c r="J168" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K168" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L168">
         <v>1</v>
@@ -9605,10 +9605,10 @@
         <v>369</v>
       </c>
       <c r="J169" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K169" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L169">
         <v>1</v>
@@ -9652,10 +9652,10 @@
         <v>361</v>
       </c>
       <c r="J170" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K170" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L170">
         <v>1</v>
@@ -9746,10 +9746,10 @@
         <v>361</v>
       </c>
       <c r="J172" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K172" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L172">
         <v>1</v>
@@ -9840,10 +9840,10 @@
         <v>370</v>
       </c>
       <c r="J174" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K174" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L174">
         <v>1</v>
@@ -9887,10 +9887,10 @@
         <v>370</v>
       </c>
       <c r="J175" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K175" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L175">
         <v>1</v>
@@ -9934,10 +9934,10 @@
         <v>362</v>
       </c>
       <c r="J176" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K176" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L176">
         <v>1</v>
@@ -9981,10 +9981,10 @@
         <v>361</v>
       </c>
       <c r="J177" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K177" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L177">
         <v>1</v>
@@ -10028,10 +10028,10 @@
         <v>364</v>
       </c>
       <c r="J178" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K178" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L178">
         <v>0</v>
@@ -10075,10 +10075,10 @@
         <v>361</v>
       </c>
       <c r="J179" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K179" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L179">
         <v>1</v>
@@ -10122,10 +10122,10 @@
         <v>362</v>
       </c>
       <c r="J180" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K180" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L180">
         <v>1</v>
@@ -10216,10 +10216,10 @@
         <v>376</v>
       </c>
       <c r="J182" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K182" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L182">
         <v>0</v>
@@ -10263,10 +10263,10 @@
         <v>361</v>
       </c>
       <c r="J183" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K183" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L183">
         <v>1</v>
@@ -10310,10 +10310,10 @@
         <v>363</v>
       </c>
       <c r="J184" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K184" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L184">
         <v>0</v>
@@ -10357,10 +10357,10 @@
         <v>373</v>
       </c>
       <c r="J185" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K185" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L185">
         <v>0</v>
@@ -10404,10 +10404,10 @@
         <v>361</v>
       </c>
       <c r="J186" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K186" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L186">
         <v>1</v>
@@ -10451,10 +10451,10 @@
         <v>362</v>
       </c>
       <c r="J187" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K187" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L187">
         <v>1</v>
@@ -10545,10 +10545,10 @@
         <v>361</v>
       </c>
       <c r="J189" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K189" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L189">
         <v>1</v>
@@ -10592,10 +10592,10 @@
         <v>369</v>
       </c>
       <c r="J190" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K190" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L190">
         <v>1</v>
@@ -10639,10 +10639,10 @@
         <v>370</v>
       </c>
       <c r="J191" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K191" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -10686,10 +10686,10 @@
         <v>361</v>
       </c>
       <c r="J192" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K192" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L192">
         <v>1</v>
@@ -10733,10 +10733,10 @@
         <v>373</v>
       </c>
       <c r="J193" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K193" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L193">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>370</v>
       </c>
       <c r="J194" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K194" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L194">
         <v>1</v>
@@ -10827,10 +10827,10 @@
         <v>361</v>
       </c>
       <c r="J195" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K195" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L195">
         <v>1</v>
@@ -10874,10 +10874,10 @@
         <v>362</v>
       </c>
       <c r="J196" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K196" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L196">
         <v>1</v>
@@ -10921,10 +10921,10 @@
         <v>377</v>
       </c>
       <c r="J197" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K197" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L197">
         <v>0</v>
@@ -11015,10 +11015,10 @@
         <v>363</v>
       </c>
       <c r="J199" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K199" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L199">
         <v>0</v>
@@ -11109,10 +11109,10 @@
         <v>361</v>
       </c>
       <c r="J201" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K201" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L201">
         <v>1</v>
@@ -11156,10 +11156,10 @@
         <v>362</v>
       </c>
       <c r="J202" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K202" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L202">
         <v>1</v>
@@ -11203,10 +11203,10 @@
         <v>362</v>
       </c>
       <c r="J203" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K203" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L203">
         <v>1</v>
@@ -11297,10 +11297,10 @@
         <v>373</v>
       </c>
       <c r="J205" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K205" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L205">
         <v>0</v>
@@ -11344,10 +11344,10 @@
         <v>370</v>
       </c>
       <c r="J206" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K206" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L206">
         <v>1</v>
@@ -11391,10 +11391,10 @@
         <v>373</v>
       </c>
       <c r="J207" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K207" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L207">
         <v>0</v>
@@ -11485,10 +11485,10 @@
         <v>370</v>
       </c>
       <c r="J209" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K209" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L209">
         <v>1</v>
@@ -11532,10 +11532,10 @@
         <v>370</v>
       </c>
       <c r="J210" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K210" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L210">
         <v>1</v>
@@ -11579,10 +11579,10 @@
         <v>378</v>
       </c>
       <c r="J211" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K211" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -11626,10 +11626,10 @@
         <v>370</v>
       </c>
       <c r="J212" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K212" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L212">
         <v>1</v>
@@ -11720,10 +11720,10 @@
         <v>370</v>
       </c>
       <c r="J214" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K214" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L214">
         <v>1</v>
@@ -11767,10 +11767,10 @@
         <v>361</v>
       </c>
       <c r="J215" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K215" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L215">
         <v>1</v>
@@ -11814,10 +11814,10 @@
         <v>364</v>
       </c>
       <c r="J216" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K216" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L216">
         <v>0</v>
@@ -11908,10 +11908,10 @@
         <v>361</v>
       </c>
       <c r="J218" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K218" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L218">
         <v>1</v>
@@ -11955,10 +11955,10 @@
         <v>363</v>
       </c>
       <c r="J219" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K219" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L219">
         <v>0</v>
@@ -12049,10 +12049,10 @@
         <v>370</v>
       </c>
       <c r="J221" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K221" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L221">
         <v>1</v>
@@ -12096,10 +12096,10 @@
         <v>361</v>
       </c>
       <c r="J222" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K222" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L222">
         <v>1</v>
@@ -12143,10 +12143,10 @@
         <v>373</v>
       </c>
       <c r="J223" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K223" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L223">
         <v>0</v>
@@ -12190,10 +12190,10 @@
         <v>370</v>
       </c>
       <c r="J224" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K224" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L224">
         <v>1</v>
@@ -12237,10 +12237,10 @@
         <v>362</v>
       </c>
       <c r="J225" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K225" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L225">
         <v>1</v>
@@ -12284,10 +12284,10 @@
         <v>369</v>
       </c>
       <c r="J226" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K226" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L226">
         <v>1</v>
@@ -12331,10 +12331,10 @@
         <v>370</v>
       </c>
       <c r="J227" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K227" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L227">
         <v>1</v>
@@ -12378,10 +12378,10 @@
         <v>370</v>
       </c>
       <c r="J228" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K228" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L228">
         <v>1</v>
@@ -12425,10 +12425,10 @@
         <v>361</v>
       </c>
       <c r="J229" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K229" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L229">
         <v>1</v>
@@ -12472,10 +12472,10 @@
         <v>370</v>
       </c>
       <c r="J230" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K230" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L230">
         <v>1</v>
@@ -12519,10 +12519,10 @@
         <v>364</v>
       </c>
       <c r="J231" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K231" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L231">
         <v>0</v>
@@ -12613,10 +12613,10 @@
         <v>364</v>
       </c>
       <c r="J233" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K233" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -12660,10 +12660,10 @@
         <v>370</v>
       </c>
       <c r="J234" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K234" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L234">
         <v>1</v>
@@ -12754,10 +12754,10 @@
         <v>364</v>
       </c>
       <c r="J236" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K236" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L236">
         <v>0</v>
@@ -12801,10 +12801,10 @@
         <v>363</v>
       </c>
       <c r="J237" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K237" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L237">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>364</v>
       </c>
       <c r="J238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K238" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L238">
         <v>0</v>
@@ -12895,10 +12895,10 @@
         <v>364</v>
       </c>
       <c r="J239" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K239" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L239">
         <v>0</v>
@@ -12942,10 +12942,10 @@
         <v>364</v>
       </c>
       <c r="J240" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K240" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L240">
         <v>0</v>
@@ -12989,10 +12989,10 @@
         <v>366</v>
       </c>
       <c r="J241" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K241" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L241">
         <v>0</v>
@@ -13036,10 +13036,10 @@
         <v>361</v>
       </c>
       <c r="J242" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K242" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L242">
         <v>1</v>
@@ -13130,10 +13130,10 @@
         <v>370</v>
       </c>
       <c r="J244" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K244" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L244">
         <v>1</v>
@@ -13177,10 +13177,10 @@
         <v>379</v>
       </c>
       <c r="J245" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K245" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L245">
         <v>0</v>
@@ -13224,10 +13224,10 @@
         <v>370</v>
       </c>
       <c r="J246" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K246" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L246">
         <v>1</v>
@@ -13271,10 +13271,10 @@
         <v>364</v>
       </c>
       <c r="J247" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K247" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>361</v>
       </c>
       <c r="J248" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K248" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L248">
         <v>1</v>
@@ -13365,10 +13365,10 @@
         <v>373</v>
       </c>
       <c r="J249" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K249" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -13412,10 +13412,10 @@
         <v>377</v>
       </c>
       <c r="J250" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K250" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -13506,10 +13506,10 @@
         <v>367</v>
       </c>
       <c r="J252" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K252" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -13600,10 +13600,10 @@
         <v>370</v>
       </c>
       <c r="J254" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K254" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L254">
         <v>1</v>
@@ -13647,10 +13647,10 @@
         <v>364</v>
       </c>
       <c r="J255" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K255" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L255">
         <v>0</v>
@@ -13694,10 +13694,10 @@
         <v>380</v>
       </c>
       <c r="J256" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K256" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L256">
         <v>0</v>
@@ -13741,10 +13741,10 @@
         <v>369</v>
       </c>
       <c r="J257" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K257" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L257">
         <v>1</v>
@@ -13788,10 +13788,10 @@
         <v>361</v>
       </c>
       <c r="J258" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K258" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L258">
         <v>1</v>
@@ -13835,10 +13835,10 @@
         <v>381</v>
       </c>
       <c r="J259" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K259" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L259">
         <v>0</v>
@@ -13882,10 +13882,10 @@
         <v>361</v>
       </c>
       <c r="J260" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K260" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L260">
         <v>1</v>
@@ -13929,10 +13929,10 @@
         <v>382</v>
       </c>
       <c r="J261" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K261" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L261">
         <v>1</v>
@@ -13976,10 +13976,10 @@
         <v>377</v>
       </c>
       <c r="J262" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K262" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -14023,10 +14023,10 @@
         <v>363</v>
       </c>
       <c r="J263" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K263" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -14070,10 +14070,10 @@
         <v>362</v>
       </c>
       <c r="J264" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K264" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L264">
         <v>1</v>
@@ -14117,10 +14117,10 @@
         <v>361</v>
       </c>
       <c r="J265" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K265" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L265">
         <v>1</v>
@@ -14164,10 +14164,10 @@
         <v>362</v>
       </c>
       <c r="J266" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K266" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L266">
         <v>1</v>
@@ -14211,10 +14211,10 @@
         <v>369</v>
       </c>
       <c r="J267" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K267" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L267">
         <v>1</v>
@@ -14258,10 +14258,10 @@
         <v>369</v>
       </c>
       <c r="J268" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K268" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L268">
         <v>1</v>
@@ -14305,10 +14305,10 @@
         <v>362</v>
       </c>
       <c r="J269" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K269" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L269">
         <v>1</v>
@@ -14352,10 +14352,10 @@
         <v>362</v>
       </c>
       <c r="J270" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K270" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L270">
         <v>1</v>
@@ -14399,10 +14399,10 @@
         <v>364</v>
       </c>
       <c r="J271" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K271" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -14446,10 +14446,10 @@
         <v>364</v>
       </c>
       <c r="J272" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K272" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -14493,10 +14493,10 @@
         <v>361</v>
       </c>
       <c r="J273" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K273" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L273">
         <v>1</v>
@@ -14540,10 +14540,10 @@
         <v>361</v>
       </c>
       <c r="J274" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K274" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L274">
         <v>1</v>
@@ -14634,10 +14634,10 @@
         <v>361</v>
       </c>
       <c r="J276" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K276" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L276">
         <v>1</v>
@@ -14681,10 +14681,10 @@
         <v>380</v>
       </c>
       <c r="J277" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K277" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -14728,10 +14728,10 @@
         <v>370</v>
       </c>
       <c r="J278" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K278" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L278">
         <v>1</v>
@@ -14822,10 +14822,10 @@
         <v>373</v>
       </c>
       <c r="J280" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K280" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -14869,10 +14869,10 @@
         <v>370</v>
       </c>
       <c r="J281" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K281" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L281">
         <v>1</v>
@@ -14916,10 +14916,10 @@
         <v>364</v>
       </c>
       <c r="J282" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K282" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -14963,10 +14963,10 @@
         <v>369</v>
       </c>
       <c r="J283" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K283" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L283">
         <v>1</v>
@@ -15010,10 +15010,10 @@
         <v>369</v>
       </c>
       <c r="J284" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K284" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L284">
         <v>1</v>
@@ -15057,10 +15057,10 @@
         <v>383</v>
       </c>
       <c r="J285" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K285" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L285">
         <v>0</v>
@@ -15104,10 +15104,10 @@
         <v>373</v>
       </c>
       <c r="J286" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K286" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L286">
         <v>0</v>
@@ -15151,10 +15151,10 @@
         <v>377</v>
       </c>
       <c r="J287" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K287" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L287">
         <v>0</v>
@@ -15198,10 +15198,10 @@
         <v>370</v>
       </c>
       <c r="J288" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K288" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L288">
         <v>1</v>
@@ -15245,10 +15245,10 @@
         <v>364</v>
       </c>
       <c r="J289" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K289" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L289">
         <v>0</v>
@@ -15292,10 +15292,10 @@
         <v>362</v>
       </c>
       <c r="J290" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K290" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L290">
         <v>1</v>
@@ -15339,10 +15339,10 @@
         <v>369</v>
       </c>
       <c r="J291" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K291" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L291">
         <v>1</v>
@@ -15433,10 +15433,10 @@
         <v>370</v>
       </c>
       <c r="J293" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K293" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L293">
         <v>1</v>
@@ -15480,10 +15480,10 @@
         <v>380</v>
       </c>
       <c r="J294" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K294" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L294">
         <v>0</v>
@@ -15527,10 +15527,10 @@
         <v>382</v>
       </c>
       <c r="J295" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K295" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L295">
         <v>1</v>
@@ -15574,10 +15574,10 @@
         <v>361</v>
       </c>
       <c r="J296" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K296" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L296">
         <v>1</v>
@@ -15621,10 +15621,10 @@
         <v>370</v>
       </c>
       <c r="J297" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K297" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L297">
         <v>1</v>
@@ -15715,10 +15715,10 @@
         <v>369</v>
       </c>
       <c r="J299" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K299" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L299">
         <v>1</v>
@@ -15762,10 +15762,10 @@
         <v>364</v>
       </c>
       <c r="J300" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K300" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L300">
         <v>0</v>
@@ -15809,10 +15809,10 @@
         <v>370</v>
       </c>
       <c r="J301" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K301" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L301">
         <v>1</v>
@@ -15856,10 +15856,10 @@
         <v>367</v>
       </c>
       <c r="J302" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K302" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L302">
         <v>0</v>
@@ -15903,10 +15903,10 @@
         <v>361</v>
       </c>
       <c r="J303" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K303" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L303">
         <v>1</v>
@@ -15950,10 +15950,10 @@
         <v>361</v>
       </c>
       <c r="J304" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K304" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L304">
         <v>1</v>
@@ -15997,10 +15997,10 @@
         <v>380</v>
       </c>
       <c r="J305" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K305" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L305">
         <v>0</v>
@@ -16044,10 +16044,10 @@
         <v>369</v>
       </c>
       <c r="J306" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K306" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L306">
         <v>1</v>
@@ -16091,10 +16091,10 @@
         <v>361</v>
       </c>
       <c r="J307" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K307" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L307">
         <v>1</v>
@@ -16138,10 +16138,10 @@
         <v>383</v>
       </c>
       <c r="J308" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K308" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L308">
         <v>0</v>
@@ -16185,10 +16185,10 @@
         <v>373</v>
       </c>
       <c r="J309" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K309" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L309">
         <v>0</v>
@@ -16232,10 +16232,10 @@
         <v>364</v>
       </c>
       <c r="J310" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K310" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L310">
         <v>0</v>
@@ -16326,10 +16326,10 @@
         <v>361</v>
       </c>
       <c r="J312" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K312" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L312">
         <v>1</v>
@@ -16373,10 +16373,10 @@
         <v>370</v>
       </c>
       <c r="J313" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K313" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L313">
         <v>1</v>
@@ -16420,10 +16420,10 @@
         <v>364</v>
       </c>
       <c r="J314" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K314" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L314">
         <v>0</v>
@@ -16467,10 +16467,10 @@
         <v>378</v>
       </c>
       <c r="J315" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K315" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L315">
         <v>0</v>
@@ -16514,10 +16514,10 @@
         <v>361</v>
       </c>
       <c r="J316" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K316" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L316">
         <v>1</v>
@@ -16561,10 +16561,10 @@
         <v>361</v>
       </c>
       <c r="J317" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K317" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L317">
         <v>1</v>
@@ -16608,10 +16608,10 @@
         <v>377</v>
       </c>
       <c r="J318" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K318" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L318">
         <v>0</v>
@@ -16655,10 +16655,10 @@
         <v>381</v>
       </c>
       <c r="J319" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K319" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L319">
         <v>0</v>
@@ -16702,10 +16702,10 @@
         <v>361</v>
       </c>
       <c r="J320" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K320" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L320">
         <v>1</v>
@@ -16749,10 +16749,10 @@
         <v>361</v>
       </c>
       <c r="J321" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K321" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L321">
         <v>1</v>
@@ -16796,10 +16796,10 @@
         <v>361</v>
       </c>
       <c r="J322" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K322" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L322">
         <v>1</v>
@@ -16843,10 +16843,10 @@
         <v>368</v>
       </c>
       <c r="J323" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K323" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L323">
         <v>0</v>
@@ -16890,10 +16890,10 @@
         <v>361</v>
       </c>
       <c r="J324" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K324" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L324">
         <v>1</v>
@@ -16937,10 +16937,10 @@
         <v>370</v>
       </c>
       <c r="J325" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K325" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L325">
         <v>1</v>
@@ -16984,10 +16984,10 @@
         <v>361</v>
       </c>
       <c r="J326" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K326" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L326">
         <v>1</v>
@@ -17031,10 +17031,10 @@
         <v>381</v>
       </c>
       <c r="J327" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K327" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L327">
         <v>0</v>
@@ -17078,10 +17078,10 @@
         <v>368</v>
       </c>
       <c r="J328" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K328" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L328">
         <v>0</v>
@@ -17125,10 +17125,10 @@
         <v>378</v>
       </c>
       <c r="J329" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K329" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L329">
         <v>0</v>
@@ -17172,10 +17172,10 @@
         <v>369</v>
       </c>
       <c r="J330" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K330" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L330">
         <v>1</v>
@@ -17219,10 +17219,10 @@
         <v>378</v>
       </c>
       <c r="J331" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K331" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L331">
         <v>0</v>
@@ -17266,10 +17266,10 @@
         <v>364</v>
       </c>
       <c r="J332" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K332" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L332">
         <v>0</v>
@@ -17313,10 +17313,10 @@
         <v>363</v>
       </c>
       <c r="J333" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K333" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L333">
         <v>0</v>
@@ -17360,10 +17360,10 @@
         <v>378</v>
       </c>
       <c r="J334" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K334" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L334">
         <v>0</v>
@@ -17407,10 +17407,10 @@
         <v>370</v>
       </c>
       <c r="J335" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K335" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L335">
         <v>1</v>
@@ -17454,10 +17454,10 @@
         <v>361</v>
       </c>
       <c r="J336" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K336" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L336">
         <v>1</v>
@@ -17501,10 +17501,10 @@
         <v>382</v>
       </c>
       <c r="J337" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K337" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L337">
         <v>1</v>
@@ -17548,10 +17548,10 @@
         <v>370</v>
       </c>
       <c r="J338" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K338" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L338">
         <v>1</v>
@@ -17595,10 +17595,10 @@
         <v>378</v>
       </c>
       <c r="J339" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K339" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L339">
         <v>0</v>
@@ -17642,10 +17642,10 @@
         <v>361</v>
       </c>
       <c r="J340" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K340" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L340">
         <v>1</v>
@@ -17689,10 +17689,10 @@
         <v>377</v>
       </c>
       <c r="J341" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K341" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L341">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>361</v>
       </c>
       <c r="J342" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K342" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L342">
         <v>1</v>
@@ -17783,10 +17783,10 @@
         <v>367</v>
       </c>
       <c r="J343" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K343" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L343">
         <v>0</v>
@@ -17830,10 +17830,10 @@
         <v>361</v>
       </c>
       <c r="J344" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K344" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L344">
         <v>1</v>
@@ -17877,10 +17877,10 @@
         <v>361</v>
       </c>
       <c r="J345" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K345" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L345">
         <v>1</v>
@@ -17924,10 +17924,10 @@
         <v>380</v>
       </c>
       <c r="J346" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K346" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L346">
         <v>0</v>
@@ -17971,10 +17971,10 @@
         <v>384</v>
       </c>
       <c r="J347" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K347" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L347">
         <v>1</v>
@@ -18018,10 +18018,10 @@
         <v>361</v>
       </c>
       <c r="J348" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K348" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L348">
         <v>1</v>
@@ -18065,10 +18065,10 @@
         <v>362</v>
       </c>
       <c r="J349" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K349" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L349">
         <v>1</v>
@@ -18112,10 +18112,10 @@
         <v>369</v>
       </c>
       <c r="J350" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K350" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L350">
         <v>1</v>
@@ -18159,10 +18159,10 @@
         <v>362</v>
       </c>
       <c r="J351" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K351" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L351">
         <v>1</v>
@@ -18206,10 +18206,10 @@
         <v>361</v>
       </c>
       <c r="J352" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K352" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L352">
         <v>1</v>
@@ -18253,10 +18253,10 @@
         <v>361</v>
       </c>
       <c r="J353" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K353" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L353">
         <v>1</v>
@@ -18300,10 +18300,10 @@
         <v>369</v>
       </c>
       <c r="J354" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K354" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L354">
         <v>1</v>
@@ -18347,10 +18347,10 @@
         <v>384</v>
       </c>
       <c r="J355" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K355" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L355">
         <v>1</v>
@@ -18394,10 +18394,10 @@
         <v>363</v>
       </c>
       <c r="J356" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K356" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L356">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>385</v>
       </c>
       <c r="J357" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K357" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L357">
         <v>0</v>
@@ -18488,10 +18488,10 @@
         <v>363</v>
       </c>
       <c r="J358" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K358" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L358">
         <v>0</v>
@@ -18535,10 +18535,10 @@
         <v>373</v>
       </c>
       <c r="J359" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K359" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L359">
         <v>0</v>
@@ -18582,10 +18582,10 @@
         <v>361</v>
       </c>
       <c r="J360" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K360" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L360">
         <v>1</v>
@@ -18629,10 +18629,10 @@
         <v>385</v>
       </c>
       <c r="J361" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K361" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L361">
         <v>0</v>
@@ -18676,10 +18676,10 @@
         <v>370</v>
       </c>
       <c r="J362" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K362" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L362">
         <v>1</v>
@@ -18723,10 +18723,10 @@
         <v>383</v>
       </c>
       <c r="J363" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K363" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L363">
         <v>0</v>
@@ -18770,10 +18770,10 @@
         <v>363</v>
       </c>
       <c r="J364" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K364" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L364">
         <v>0</v>
@@ -18817,10 +18817,10 @@
         <v>377</v>
       </c>
       <c r="J365" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K365" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L365">
         <v>0</v>
@@ -18864,10 +18864,10 @@
         <v>362</v>
       </c>
       <c r="J366" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K366" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L366">
         <v>1</v>
@@ -18911,10 +18911,10 @@
         <v>386</v>
       </c>
       <c r="J367" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K367" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L367">
         <v>0</v>
@@ -18958,10 +18958,10 @@
         <v>385</v>
       </c>
       <c r="J368" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K368" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L368">
         <v>0</v>
@@ -19005,10 +19005,10 @@
         <v>361</v>
       </c>
       <c r="J369" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K369" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L369">
         <v>1</v>
@@ -19052,10 +19052,10 @@
         <v>368</v>
       </c>
       <c r="J370" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K370" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L370">
         <v>0</v>
@@ -19099,10 +19099,10 @@
         <v>369</v>
       </c>
       <c r="J371" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K371" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L371">
         <v>1</v>
@@ -19146,10 +19146,10 @@
         <v>378</v>
       </c>
       <c r="J372" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K372" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L372">
         <v>0</v>
@@ -19193,10 +19193,10 @@
         <v>363</v>
       </c>
       <c r="J373" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K373" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L373">
         <v>0</v>
@@ -19240,10 +19240,10 @@
         <v>383</v>
       </c>
       <c r="J374" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K374" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L374">
         <v>0</v>
@@ -19287,10 +19287,10 @@
         <v>384</v>
       </c>
       <c r="J375" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K375" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L375">
         <v>1</v>
@@ -19334,10 +19334,10 @@
         <v>362</v>
       </c>
       <c r="J376" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K376" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L376">
         <v>1</v>
@@ -19381,10 +19381,10 @@
         <v>387</v>
       </c>
       <c r="J377" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K377" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L377">
         <v>0</v>
@@ -19428,10 +19428,10 @@
         <v>368</v>
       </c>
       <c r="J378" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K378" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L378">
         <v>0</v>
@@ -19475,10 +19475,10 @@
         <v>384</v>
       </c>
       <c r="J379" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K379" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L379">
         <v>1</v>
@@ -19522,10 +19522,10 @@
         <v>361</v>
       </c>
       <c r="J380" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K380" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L380">
         <v>1</v>
@@ -19569,10 +19569,10 @@
         <v>383</v>
       </c>
       <c r="J381" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K381" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L381">
         <v>0</v>
@@ -19616,10 +19616,10 @@
         <v>363</v>
       </c>
       <c r="J382" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K382" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L382">
         <v>0</v>
@@ -19663,10 +19663,10 @@
         <v>369</v>
       </c>
       <c r="J383" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K383" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L383">
         <v>1</v>
@@ -19710,10 +19710,10 @@
         <v>384</v>
       </c>
       <c r="J384" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K384" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L384">
         <v>1</v>
@@ -19757,10 +19757,10 @@
         <v>385</v>
       </c>
       <c r="J385" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K385" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L385">
         <v>0</v>
@@ -19804,10 +19804,10 @@
         <v>364</v>
       </c>
       <c r="J386" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K386" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L386">
         <v>0</v>
@@ -19851,10 +19851,10 @@
         <v>369</v>
       </c>
       <c r="J387" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K387" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L387">
         <v>1</v>
@@ -19898,10 +19898,10 @@
         <v>384</v>
       </c>
       <c r="J388" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K388" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L388">
         <v>1</v>
@@ -19945,10 +19945,10 @@
         <v>384</v>
       </c>
       <c r="J389" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K389" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L389">
         <v>1</v>
@@ -19992,10 +19992,10 @@
         <v>369</v>
       </c>
       <c r="J390" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K390" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L390">
         <v>1</v>
@@ -20039,10 +20039,10 @@
         <v>363</v>
       </c>
       <c r="J391" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K391" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L391">
         <v>0</v>
@@ -20086,10 +20086,10 @@
         <v>388</v>
       </c>
       <c r="J392" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K392" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L392">
         <v>1</v>
@@ -20133,10 +20133,10 @@
         <v>364</v>
       </c>
       <c r="J393" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K393" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L393">
         <v>0</v>
@@ -20180,10 +20180,10 @@
         <v>362</v>
       </c>
       <c r="J394" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K394" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L394">
         <v>1</v>
@@ -20227,10 +20227,10 @@
         <v>379</v>
       </c>
       <c r="J395" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K395" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L395">
         <v>0</v>
@@ -20274,10 +20274,10 @@
         <v>389</v>
       </c>
       <c r="J396" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K396" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L396">
         <v>0</v>
@@ -20321,10 +20321,10 @@
         <v>363</v>
       </c>
       <c r="J397" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K397" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L397">
         <v>0</v>
@@ -20368,10 +20368,10 @@
         <v>367</v>
       </c>
       <c r="J398" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K398" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L398">
         <v>0</v>
@@ -20415,10 +20415,10 @@
         <v>379</v>
       </c>
       <c r="J399" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K399" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L399">
         <v>0</v>
@@ -20462,10 +20462,10 @@
         <v>390</v>
       </c>
       <c r="J400" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K400" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L400">
         <v>0</v>
@@ -20509,10 +20509,10 @@
         <v>388</v>
       </c>
       <c r="J401" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K401" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L401">
         <v>1</v>
@@ -20556,10 +20556,10 @@
         <v>361</v>
       </c>
       <c r="J402" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K402" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L402">
         <v>1</v>
@@ -20603,10 +20603,10 @@
         <v>363</v>
       </c>
       <c r="J403" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K403" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L403">
         <v>0</v>
@@ -20650,10 +20650,10 @@
         <v>389</v>
       </c>
       <c r="J404" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K404" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L404">
         <v>0</v>
@@ -20697,10 +20697,10 @@
         <v>362</v>
       </c>
       <c r="J405" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K405" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L405">
         <v>1</v>
@@ -20744,10 +20744,10 @@
         <v>388</v>
       </c>
       <c r="J406" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K406" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L406">
         <v>1</v>
@@ -20791,10 +20791,10 @@
         <v>362</v>
       </c>
       <c r="J407" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K407" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L407">
         <v>1</v>
@@ -20838,10 +20838,10 @@
         <v>380</v>
       </c>
       <c r="J408" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K408" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L408">
         <v>0</v>
@@ -20885,10 +20885,10 @@
         <v>368</v>
       </c>
       <c r="J409" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K409" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L409">
         <v>0</v>
@@ -20932,10 +20932,10 @@
         <v>370</v>
       </c>
       <c r="J410" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K410" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L410">
         <v>1</v>
@@ -20979,10 +20979,10 @@
         <v>362</v>
       </c>
       <c r="J411" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K411" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L411">
         <v>1</v>
@@ -21026,10 +21026,10 @@
         <v>382</v>
       </c>
       <c r="J412" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K412" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L412">
         <v>1</v>
@@ -21073,10 +21073,10 @@
         <v>390</v>
       </c>
       <c r="J413" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K413" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L413">
         <v>0</v>
@@ -21120,10 +21120,10 @@
         <v>379</v>
       </c>
       <c r="J414" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K414" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L414">
         <v>0</v>
@@ -21167,10 +21167,10 @@
         <v>386</v>
       </c>
       <c r="J415" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K415" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L415">
         <v>0</v>
@@ -21214,10 +21214,10 @@
         <v>362</v>
       </c>
       <c r="J416" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K416" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L416">
         <v>1</v>
@@ -21261,10 +21261,10 @@
         <v>391</v>
       </c>
       <c r="J417" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K417" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L417">
         <v>0</v>
@@ -21308,10 +21308,10 @@
         <v>363</v>
       </c>
       <c r="J418" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K418" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L418">
         <v>0</v>
@@ -21355,10 +21355,10 @@
         <v>370</v>
       </c>
       <c r="J419" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K419" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L419">
         <v>1</v>
@@ -21402,10 +21402,10 @@
         <v>361</v>
       </c>
       <c r="J420" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K420" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L420">
         <v>1</v>
@@ -21449,10 +21449,10 @@
         <v>384</v>
       </c>
       <c r="J421" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K421" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L421">
         <v>1</v>
@@ -21496,10 +21496,10 @@
         <v>377</v>
       </c>
       <c r="J422" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K422" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L422">
         <v>0</v>
@@ -21543,10 +21543,10 @@
         <v>389</v>
       </c>
       <c r="J423" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K423" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L423">
         <v>0</v>
@@ -21590,10 +21590,10 @@
         <v>384</v>
       </c>
       <c r="J424" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K424" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L424">
         <v>1</v>
@@ -21637,10 +21637,10 @@
         <v>364</v>
       </c>
       <c r="J425" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K425" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L425">
         <v>0</v>
@@ -21684,10 +21684,10 @@
         <v>363</v>
       </c>
       <c r="J426" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K426" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L426">
         <v>0</v>
@@ -21731,10 +21731,10 @@
         <v>362</v>
       </c>
       <c r="J427" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K427" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L427">
         <v>1</v>
@@ -21778,10 +21778,10 @@
         <v>363</v>
       </c>
       <c r="J428" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K428" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L428">
         <v>0</v>
@@ -21825,10 +21825,10 @@
         <v>369</v>
       </c>
       <c r="J429" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K429" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L429">
         <v>1</v>
@@ -21872,10 +21872,10 @@
         <v>361</v>
       </c>
       <c r="J430" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K430" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L430">
         <v>1</v>
@@ -21919,10 +21919,10 @@
         <v>368</v>
       </c>
       <c r="J431" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K431" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L431">
         <v>0</v>
@@ -21966,10 +21966,10 @@
         <v>362</v>
       </c>
       <c r="J432" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K432" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L432">
         <v>1</v>
@@ -22013,10 +22013,10 @@
         <v>385</v>
       </c>
       <c r="J433" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K433" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L433">
         <v>0</v>
@@ -22060,10 +22060,10 @@
         <v>389</v>
       </c>
       <c r="J434" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K434" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L434">
         <v>0</v>
@@ -22107,10 +22107,10 @@
         <v>384</v>
       </c>
       <c r="J435" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K435" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L435">
         <v>1</v>
@@ -22154,10 +22154,10 @@
         <v>379</v>
       </c>
       <c r="J436" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K436" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L436">
         <v>0</v>
@@ -22201,10 +22201,10 @@
         <v>377</v>
       </c>
       <c r="J437" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K437" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L437">
         <v>0</v>
@@ -22248,10 +22248,10 @@
         <v>369</v>
       </c>
       <c r="J438" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K438" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L438">
         <v>1</v>
@@ -22295,10 +22295,10 @@
         <v>371</v>
       </c>
       <c r="J439" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K439" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L439">
         <v>1</v>
@@ -22342,10 +22342,10 @@
         <v>367</v>
       </c>
       <c r="J440" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K440" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L440">
         <v>0</v>
@@ -22389,10 +22389,10 @@
         <v>370</v>
       </c>
       <c r="J441" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K441" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L441">
         <v>1</v>
@@ -22436,10 +22436,10 @@
         <v>379</v>
       </c>
       <c r="J442" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K442" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L442">
         <v>0</v>
@@ -22483,10 +22483,10 @@
         <v>384</v>
       </c>
       <c r="J443" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K443" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L443">
         <v>1</v>
@@ -22530,10 +22530,10 @@
         <v>385</v>
       </c>
       <c r="J444" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K444" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L444">
         <v>0</v>
@@ -22577,10 +22577,10 @@
         <v>379</v>
       </c>
       <c r="J445" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K445" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L445">
         <v>0</v>
@@ -22624,10 +22624,10 @@
         <v>364</v>
       </c>
       <c r="J446" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K446" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L446">
         <v>0</v>
@@ -22671,10 +22671,10 @@
         <v>379</v>
       </c>
       <c r="J447" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K447" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L447">
         <v>0</v>
@@ -22718,10 +22718,10 @@
         <v>373</v>
       </c>
       <c r="J448" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K448" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L448">
         <v>0</v>
@@ -22765,10 +22765,10 @@
         <v>363</v>
       </c>
       <c r="J449" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K449" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L449">
         <v>0</v>
@@ -22812,10 +22812,10 @@
         <v>387</v>
       </c>
       <c r="J450" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K450" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L450">
         <v>0</v>
@@ -22859,10 +22859,10 @@
         <v>362</v>
       </c>
       <c r="J451" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K451" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L451">
         <v>1</v>
@@ -22906,10 +22906,10 @@
         <v>384</v>
       </c>
       <c r="J452" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K452" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L452">
         <v>1</v>
@@ -22953,10 +22953,10 @@
         <v>382</v>
       </c>
       <c r="J453" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K453" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L453">
         <v>1</v>
@@ -23000,10 +23000,10 @@
         <v>384</v>
       </c>
       <c r="J454" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K454" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L454">
         <v>1</v>
@@ -23047,10 +23047,10 @@
         <v>367</v>
       </c>
       <c r="J455" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K455" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L455">
         <v>0</v>
@@ -23094,10 +23094,10 @@
         <v>364</v>
       </c>
       <c r="J456" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K456" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L456">
         <v>0</v>
@@ -23141,10 +23141,10 @@
         <v>390</v>
       </c>
       <c r="J457" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K457" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L457">
         <v>0</v>
@@ -23188,10 +23188,10 @@
         <v>384</v>
       </c>
       <c r="J458" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K458" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L458">
         <v>1</v>
@@ -23235,10 +23235,10 @@
         <v>378</v>
       </c>
       <c r="J459" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K459" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L459">
         <v>0</v>
@@ -23282,10 +23282,10 @@
         <v>390</v>
       </c>
       <c r="J460" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K460" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L460">
         <v>0</v>
@@ -23329,10 +23329,10 @@
         <v>361</v>
       </c>
       <c r="J461" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K461" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L461">
         <v>1</v>
@@ -23376,10 +23376,10 @@
         <v>390</v>
       </c>
       <c r="J462" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K462" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L462">
         <v>0</v>
@@ -23423,10 +23423,10 @@
         <v>377</v>
       </c>
       <c r="J463" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K463" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L463">
         <v>0</v>
@@ -23470,10 +23470,10 @@
         <v>379</v>
       </c>
       <c r="J464" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K464" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L464">
         <v>0</v>
@@ -23517,10 +23517,10 @@
         <v>377</v>
       </c>
       <c r="J465" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K465" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L465">
         <v>0</v>
@@ -23564,10 +23564,10 @@
         <v>362</v>
       </c>
       <c r="J466" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K466" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L466">
         <v>1</v>
@@ -23611,10 +23611,10 @@
         <v>361</v>
       </c>
       <c r="J467" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K467" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L467">
         <v>1</v>
@@ -23658,10 +23658,10 @@
         <v>384</v>
       </c>
       <c r="J468" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K468" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L468">
         <v>1</v>
@@ -23705,10 +23705,10 @@
         <v>377</v>
       </c>
       <c r="J469" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K469" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L469">
         <v>0</v>
@@ -23752,10 +23752,10 @@
         <v>389</v>
       </c>
       <c r="J470" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K470" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L470">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>392</v>
       </c>
       <c r="J471" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K471" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L471">
         <v>1</v>
@@ -23846,10 +23846,10 @@
         <v>386</v>
       </c>
       <c r="J472" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K472" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L472">
         <v>0</v>
@@ -23893,10 +23893,10 @@
         <v>379</v>
       </c>
       <c r="J473" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K473" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L473">
         <v>0</v>
@@ -23940,10 +23940,10 @@
         <v>369</v>
       </c>
       <c r="J474" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K474" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L474">
         <v>1</v>
@@ -23987,10 +23987,10 @@
         <v>367</v>
       </c>
       <c r="J475" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K475" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L475">
         <v>0</v>
@@ -24034,10 +24034,10 @@
         <v>369</v>
       </c>
       <c r="J476" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K476" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L476">
         <v>1</v>
@@ -24081,10 +24081,10 @@
         <v>384</v>
       </c>
       <c r="J477" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K477" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L477">
         <v>1</v>
@@ -24128,10 +24128,10 @@
         <v>383</v>
       </c>
       <c r="J478" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K478" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L478">
         <v>0</v>
@@ -24175,10 +24175,10 @@
         <v>377</v>
       </c>
       <c r="J479" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K479" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L479">
         <v>0</v>
@@ -24222,10 +24222,10 @@
         <v>388</v>
       </c>
       <c r="J480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K480" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L480">
         <v>1</v>
@@ -24269,10 +24269,10 @@
         <v>384</v>
       </c>
       <c r="J481" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K481" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L481">
         <v>1</v>
@@ -24316,10 +24316,10 @@
         <v>363</v>
       </c>
       <c r="J482" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K482" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L482">
         <v>0</v>
@@ -24363,10 +24363,10 @@
         <v>393</v>
       </c>
       <c r="J483" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K483" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L483">
         <v>1</v>
@@ -24410,10 +24410,10 @@
         <v>384</v>
       </c>
       <c r="J484" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K484" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L484">
         <v>1</v>
@@ -24457,10 +24457,10 @@
         <v>386</v>
       </c>
       <c r="J485" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K485" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L485">
         <v>0</v>
@@ -24504,10 +24504,10 @@
         <v>383</v>
       </c>
       <c r="J486" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K486" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L486">
         <v>0</v>
@@ -24551,10 +24551,10 @@
         <v>361</v>
       </c>
       <c r="J487" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K487" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L487">
         <v>1</v>
@@ -24598,10 +24598,10 @@
         <v>382</v>
       </c>
       <c r="J488" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K488" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L488">
         <v>1</v>
@@ -24645,10 +24645,10 @@
         <v>393</v>
       </c>
       <c r="J489" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K489" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L489">
         <v>1</v>
@@ -24692,10 +24692,10 @@
         <v>362</v>
       </c>
       <c r="J490" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K490" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L490">
         <v>1</v>
@@ -24739,10 +24739,10 @@
         <v>394</v>
       </c>
       <c r="J491" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K491" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L491">
         <v>1</v>
@@ -24786,10 +24786,10 @@
         <v>382</v>
       </c>
       <c r="J492" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K492" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L492">
         <v>1</v>
@@ -24833,10 +24833,10 @@
         <v>386</v>
       </c>
       <c r="J493" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K493" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L493">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>384</v>
       </c>
       <c r="J494" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K494" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L494">
         <v>1</v>
@@ -24927,10 +24927,10 @@
         <v>389</v>
       </c>
       <c r="J495" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K495" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L495">
         <v>0</v>
@@ -24971,13 +24971,13 @@
         <v>1.341123022891294E-2</v>
       </c>
       <c r="I496" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="J496" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K496" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L496">
         <v>1</v>
@@ -25021,10 +25021,10 @@
         <v>370</v>
       </c>
       <c r="J497" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K497" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L497">
         <v>1</v>
@@ -25068,10 +25068,10 @@
         <v>382</v>
       </c>
       <c r="J498" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K498" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L498">
         <v>1</v>
@@ -25115,10 +25115,10 @@
         <v>377</v>
       </c>
       <c r="J499" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L499">
         <v>0</v>
@@ -25162,10 +25162,10 @@
         <v>371</v>
       </c>
       <c r="J500" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K500" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L500">
         <v>1</v>
@@ -25209,10 +25209,10 @@
         <v>389</v>
       </c>
       <c r="J501" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K501" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L501">
         <v>0</v>
@@ -25256,10 +25256,10 @@
         <v>362</v>
       </c>
       <c r="J502" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K502" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L502">
         <v>1</v>
@@ -25303,10 +25303,10 @@
         <v>363</v>
       </c>
       <c r="J503" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K503" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L503">
         <v>0</v>
@@ -25350,10 +25350,10 @@
         <v>370</v>
       </c>
       <c r="J504" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L504">
         <v>1</v>
@@ -25397,10 +25397,10 @@
         <v>361</v>
       </c>
       <c r="J505" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K505" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L505">
         <v>1</v>
@@ -25444,10 +25444,10 @@
         <v>361</v>
       </c>
       <c r="J506" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K506" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L506">
         <v>1</v>
@@ -25491,10 +25491,10 @@
         <v>379</v>
       </c>
       <c r="J507" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K507" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L507">
         <v>0</v>
@@ -25538,10 +25538,10 @@
         <v>362</v>
       </c>
       <c r="J508" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K508" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L508">
         <v>1</v>
@@ -25585,10 +25585,10 @@
         <v>384</v>
       </c>
       <c r="J509" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K509" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L509">
         <v>1</v>
@@ -25632,10 +25632,10 @@
         <v>362</v>
       </c>
       <c r="J510" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K510" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L510">
         <v>1</v>
@@ -25679,10 +25679,10 @@
         <v>373</v>
       </c>
       <c r="J511" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K511" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L511">
         <v>0</v>
@@ -25726,10 +25726,10 @@
         <v>361</v>
       </c>
       <c r="J512" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K512" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L512">
         <v>1</v>
@@ -25773,10 +25773,10 @@
         <v>382</v>
       </c>
       <c r="J513" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K513" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L513">
         <v>1</v>
@@ -25820,10 +25820,10 @@
         <v>384</v>
       </c>
       <c r="J514" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K514" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L514">
         <v>1</v>
@@ -25867,10 +25867,10 @@
         <v>361</v>
       </c>
       <c r="J515" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K515" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L515">
         <v>1</v>
@@ -25914,10 +25914,10 @@
         <v>382</v>
       </c>
       <c r="J516" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K516" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L516">
         <v>1</v>
@@ -25961,10 +25961,10 @@
         <v>382</v>
       </c>
       <c r="J517" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K517" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L517">
         <v>1</v>
@@ -26008,10 +26008,10 @@
         <v>361</v>
       </c>
       <c r="J518" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K518" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L518">
         <v>1</v>
@@ -26055,10 +26055,10 @@
         <v>381</v>
       </c>
       <c r="J519" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K519" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L519">
         <v>0</v>
@@ -26099,13 +26099,13 @@
         <v>5.2471114791511058E-4</v>
       </c>
       <c r="I520" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J520" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K520" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L520">
         <v>1</v>
@@ -26146,13 +26146,13 @@
         <v>0</v>
       </c>
       <c r="I521" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J521" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K521" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L521">
         <v>0</v>
@@ -26193,13 +26193,13 @@
         <v>0</v>
       </c>
       <c r="I522" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J522" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K522" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L522">
         <v>1</v>
@@ -26243,10 +26243,10 @@
         <v>389</v>
       </c>
       <c r="J523" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K523" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L523">
         <v>0</v>
@@ -26290,10 +26290,10 @@
         <v>362</v>
       </c>
       <c r="J524" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K524" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L524">
         <v>1</v>
@@ -26337,10 +26337,10 @@
         <v>381</v>
       </c>
       <c r="J525" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K525" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L525">
         <v>0</v>
@@ -26384,10 +26384,10 @@
         <v>382</v>
       </c>
       <c r="J526" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K526" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L526">
         <v>1</v>
@@ -26431,10 +26431,10 @@
         <v>381</v>
       </c>
       <c r="J527" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K527" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L527">
         <v>0</v>
@@ -26475,13 +26475,13 @@
         <v>93.23348362847878</v>
       </c>
       <c r="I528" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J528" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K528" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L528">
         <v>1</v>
@@ -26525,10 +26525,10 @@
         <v>363</v>
       </c>
       <c r="J529" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K529" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L529">
         <v>0</v>
@@ -26572,10 +26572,10 @@
         <v>381</v>
       </c>
       <c r="J530" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K530" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L530">
         <v>0</v>
@@ -26619,10 +26619,10 @@
         <v>370</v>
       </c>
       <c r="J531" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K531" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L531">
         <v>1</v>
@@ -26666,10 +26666,10 @@
         <v>379</v>
       </c>
       <c r="J532" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K532" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L532">
         <v>0</v>
@@ -26713,10 +26713,10 @@
         <v>367</v>
       </c>
       <c r="J533" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K533" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L533">
         <v>0</v>
@@ -26760,10 +26760,10 @@
         <v>363</v>
       </c>
       <c r="J534" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K534" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L534">
         <v>0</v>
@@ -26804,13 +26804,13 @@
         <v>1.1659276193378199E-3</v>
       </c>
       <c r="I535" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J535" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K535" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L535">
         <v>1</v>
@@ -26854,10 +26854,10 @@
         <v>362</v>
       </c>
       <c r="J536" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K536" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L536">
         <v>1</v>
@@ -26901,10 +26901,10 @@
         <v>369</v>
       </c>
       <c r="J537" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K537" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L537">
         <v>1</v>
@@ -26945,13 +26945,13 @@
         <v>9.2480481422883159E-4</v>
       </c>
       <c r="I538" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J538" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K538" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L538">
         <v>1</v>
@@ -26992,13 +26992,13 @@
         <v>1.570608308732915E-2</v>
       </c>
       <c r="I539" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J539" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K539" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L539">
         <v>1</v>
@@ -27042,10 +27042,10 @@
         <v>362</v>
       </c>
       <c r="J540" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K540" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L540">
         <v>1</v>
@@ -27086,13 +27086,13 @@
         <v>2.9222557652352852E-3</v>
       </c>
       <c r="I541" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J541" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K541" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L541">
         <v>1</v>
@@ -27133,13 +27133,13 @@
         <v>9.1731266149870798</v>
       </c>
       <c r="I542" t="s">
+        <v>401</v>
+      </c>
+      <c r="J542" t="s">
         <v>402</v>
       </c>
-      <c r="J542" t="s">
-        <v>403</v>
-      </c>
       <c r="K542" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L542">
         <v>1</v>
@@ -27183,10 +27183,10 @@
         <v>382</v>
       </c>
       <c r="J543" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K543" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L543">
         <v>1</v>

--- a/pandemic-loss-modeling/data/epidemics_marani_240816.xlsx
+++ b/pandemic-loss-modeling/data/epidemics_marani_240816.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lichong/Desktop/RA 23F Epidemic/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lichong/Documents/GitHub/pandemic-loss-modeling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2295CB99-6C51-4040-B16A-D8FC83BA3A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B064693-7C84-1F48-A10F-EEEDEE732B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="22620" windowHeight="14420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="430">
   <si>
     <t>location</t>
   </si>
@@ -1677,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:O542"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -27154,53 +27154,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A543" t="s">
-        <v>38</v>
-      </c>
-      <c r="B543">
-        <v>2023</v>
-      </c>
-      <c r="C543">
-        <v>2023</v>
-      </c>
-      <c r="D543">
-        <v>1</v>
-      </c>
-      <c r="E543">
-        <v>4</v>
-      </c>
-      <c r="F543">
-        <v>8020000</v>
-      </c>
-      <c r="G543">
-        <v>4.9875311720698251E-4</v>
-      </c>
-      <c r="H543">
-        <v>4.9875311720698253E-3</v>
-      </c>
-      <c r="I543" t="s">
-        <v>382</v>
-      </c>
-      <c r="J543" t="s">
-        <v>402</v>
-      </c>
-      <c r="K543" t="s">
-        <v>415</v>
-      </c>
-      <c r="L543">
-        <v>1</v>
-      </c>
-      <c r="M543">
-        <v>0</v>
-      </c>
-      <c r="N543">
-        <v>1</v>
-      </c>
-      <c r="O543">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
